--- a/ig/DM-JUIN-2026/ValueSet-JDV-J33-CompetenceSpecifique-ROR.xlsx
+++ b/ig/DM-JUIN-2026/ValueSet-JDV-J33-CompetenceSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="145">
   <si>
     <t>Property</t>
   </si>
@@ -439,9 +439,6 @@
   </si>
   <si>
     <t>Maitrise des outils informatisés à commande oculaire</t>
-  </si>
-  <si>
-    <t>64</t>
   </si>
   <si>
     <t/>
@@ -712,7 +709,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1188,7 +1185,7 @@
         <v>142</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="60">
@@ -1196,15 +1193,7 @@
         <v>143</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>145</v>
       </c>
     </row>
   </sheetData>
